--- a/sample_data/demo_liquidacion_datprod.xlsx
+++ b/sample_data/demo_liquidacion_datprod.xlsx
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="O2" s="1" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>46670</v>
+        <v>46672</v>
       </c>
     </row>
   </sheetData>
